--- a/mlb_weather_professional_2026_07_10.xlsx
+++ b/mlb_weather_professional_2026_07_10.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="457">
   <si>
     <t>Date</t>
   </si>
@@ -854,43 +854,46 @@
     <t>C</t>
   </si>
   <si>
-    <t>2026-07-10 02:23:15 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:16 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:17 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:18 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:19 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:20 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:21 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:22 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:23 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:24 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:25 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:26 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-10 02:23:27 PM PDT</t>
+    <t>2026-07-10 02:24:03 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:04 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:05 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:06 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:07 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:08 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:09 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:10 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:11 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:12 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:13 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:14 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:15 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-10 02:24:16 PM PDT</t>
   </si>
   <si>
     <t>MODERATE</t>
@@ -971,43 +974,46 @@
     <t>Clear</t>
   </si>
   <si>
-    <t>2026-07-10 21:23:15 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:16 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:17 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:18 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:19 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:20 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:21 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:22 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:23 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 21:23:27 UTC</t>
+    <t>2026-07-10 21:24:03 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:04 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:05 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:06 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:07 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:08 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:09 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:10 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:11 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:12 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:13 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:14 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:15 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-10 21:24:16 UTC</t>
   </si>
   <si>
     <t>2026-07-10T20:25:01+00:00</t>
@@ -2507,7 +2513,7 @@
         <v>277</v>
       </c>
       <c r="W2">
-        <v>58.2</v>
+        <v>59</v>
       </c>
       <c r="X2">
         <v>5</v>
@@ -2525,28 +2531,28 @@
         <v>2071</v>
       </c>
       <c r="AC2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AD2">
         <v>27.5</v>
       </c>
       <c r="AE2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF2">
         <v>6.4</v>
       </c>
       <c r="AG2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI2" t="s">
         <v>224</v>
       </c>
       <c r="AJ2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK2">
         <v>42.339</v>
@@ -2561,16 +2567,16 @@
         <v>45</v>
       </c>
       <c r="AO2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AR2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AS2">
         <v>0.92</v>
@@ -2648,7 +2654,7 @@
         <v>7.1</v>
       </c>
       <c r="BR2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="BS2">
         <v>-3.7</v>
@@ -2690,7 +2696,7 @@
         <v>23.2</v>
       </c>
       <c r="CF2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG2">
         <v>78.7</v>
@@ -2717,7 +2723,7 @@
         <v>7.4</v>
       </c>
       <c r="CO2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="CP2">
         <v>-4.4</v>
@@ -2759,7 +2765,7 @@
         <v>21.9</v>
       </c>
       <c r="DC2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD2">
         <v>76.59999999999999</v>
@@ -2786,7 +2792,7 @@
         <v>9.1</v>
       </c>
       <c r="DL2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="DM2">
         <v>-5</v>
@@ -2828,7 +2834,7 @@
         <v>19.1</v>
       </c>
       <c r="DZ2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA2">
         <v>74.09999999999999</v>
@@ -2855,7 +2861,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="EI2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="EJ2">
         <v>-4.5</v>
@@ -2897,7 +2903,7 @@
         <v>27.5</v>
       </c>
       <c r="EW2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EX2">
         <v>47</v>
@@ -2971,7 +2977,7 @@
         <v>278</v>
       </c>
       <c r="W3">
-        <v>181.6</v>
+        <v>182.4</v>
       </c>
       <c r="X3">
         <v>5</v>
@@ -2989,28 +2995,28 @@
         <v>2181</v>
       </c>
       <c r="AC3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AD3">
         <v>46.3</v>
       </c>
       <c r="AE3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF3">
         <v>20.7</v>
       </c>
       <c r="AG3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI3" t="s">
         <v>225</v>
       </c>
       <c r="AJ3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK3">
         <v>40.4469</v>
@@ -3025,16 +3031,16 @@
         <v>45</v>
       </c>
       <c r="AO3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AQ3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AR3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AS3">
         <v>0.92</v>
@@ -3112,7 +3118,7 @@
         <v>5.9</v>
       </c>
       <c r="BR3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BS3">
         <v>3.4</v>
@@ -3154,7 +3160,7 @@
         <v>46.3</v>
       </c>
       <c r="CF3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="CG3">
         <v>75.59999999999999</v>
@@ -3181,7 +3187,7 @@
         <v>10.1</v>
       </c>
       <c r="CO3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="CP3">
         <v>2.9</v>
@@ -3223,7 +3229,7 @@
         <v>44.9</v>
       </c>
       <c r="DC3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD3">
         <v>73.90000000000001</v>
@@ -3250,7 +3256,7 @@
         <v>5.1</v>
       </c>
       <c r="DL3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="DM3">
         <v>1.2</v>
@@ -3292,7 +3298,7 @@
         <v>38.4</v>
       </c>
       <c r="DZ3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EA3">
         <v>73.09999999999999</v>
@@ -3319,7 +3325,7 @@
         <v>3.4</v>
       </c>
       <c r="EI3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="EJ3">
         <v>0.8</v>
@@ -3361,7 +3367,7 @@
         <v>27.1</v>
       </c>
       <c r="EW3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EX3">
         <v>80</v>
@@ -3435,7 +3441,7 @@
         <v>279</v>
       </c>
       <c r="W4">
-        <v>30.1</v>
+        <v>30.9</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -3453,28 +3459,28 @@
         <v>1606</v>
       </c>
       <c r="AC4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AD4">
         <v>14.9</v>
       </c>
       <c r="AE4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF4">
         <v>11.7</v>
       </c>
       <c r="AG4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI4" t="s">
         <v>226</v>
       </c>
       <c r="AJ4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK4">
         <v>38.873</v>
@@ -3489,16 +3495,16 @@
         <v>35</v>
       </c>
       <c r="AO4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AS4">
         <v>0.92</v>
@@ -3576,7 +3582,7 @@
         <v>7.8</v>
       </c>
       <c r="BR4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BS4">
         <v>2.2</v>
@@ -3618,7 +3624,7 @@
         <v>14.9</v>
       </c>
       <c r="CF4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CG4">
         <v>81.09999999999999</v>
@@ -3645,7 +3651,7 @@
         <v>5.9</v>
       </c>
       <c r="CO4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CP4">
         <v>2</v>
@@ -3687,7 +3693,7 @@
         <v>12.1</v>
       </c>
       <c r="DC4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD4">
         <v>78.90000000000001</v>
@@ -3714,7 +3720,7 @@
         <v>5.4</v>
       </c>
       <c r="DL4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="DM4">
         <v>2.3</v>
@@ -3756,7 +3762,7 @@
         <v>8.9</v>
       </c>
       <c r="DZ4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA4">
         <v>77.3</v>
@@ -3783,7 +3789,7 @@
         <v>4.5</v>
       </c>
       <c r="EI4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="EJ4">
         <v>2.7</v>
@@ -3825,7 +3831,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="EW4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX4">
         <v>73</v>
@@ -3899,7 +3905,7 @@
         <v>280</v>
       </c>
       <c r="W5">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -3917,28 +3923,28 @@
         <v>1430</v>
       </c>
       <c r="AC5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AD5">
         <v>20.9</v>
       </c>
       <c r="AE5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF5">
         <v>10.7</v>
       </c>
       <c r="AG5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI5" t="s">
         <v>227</v>
       </c>
       <c r="AJ5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK5">
         <v>39.2839</v>
@@ -3953,16 +3959,16 @@
         <v>60</v>
       </c>
       <c r="AO5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AR5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AS5">
         <v>0.92</v>
@@ -4040,7 +4046,7 @@
         <v>12.3</v>
       </c>
       <c r="BR5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BS5">
         <v>3.9</v>
@@ -4082,7 +4088,7 @@
         <v>20.9</v>
       </c>
       <c r="CF5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG5">
         <v>78.90000000000001</v>
@@ -4109,7 +4115,7 @@
         <v>8.5</v>
       </c>
       <c r="CO5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CP5">
         <v>2.2</v>
@@ -4151,7 +4157,7 @@
         <v>15.5</v>
       </c>
       <c r="DC5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD5">
         <v>77.2</v>
@@ -4178,7 +4184,7 @@
         <v>7</v>
       </c>
       <c r="DL5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="DM5">
         <v>1.7</v>
@@ -4220,7 +4226,7 @@
         <v>11.2</v>
       </c>
       <c r="DZ5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA5">
         <v>75.8</v>
@@ -4247,7 +4253,7 @@
         <v>4.6</v>
       </c>
       <c r="EI5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="EJ5">
         <v>1.9</v>
@@ -4289,7 +4295,7 @@
         <v>9</v>
       </c>
       <c r="EW5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX5">
         <v>67</v>
@@ -4363,7 +4369,7 @@
         <v>281</v>
       </c>
       <c r="W6">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -4381,28 +4387,28 @@
         <v>2406</v>
       </c>
       <c r="AC6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AD6">
         <v>29.1</v>
       </c>
       <c r="AE6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF6">
         <v>10.5</v>
       </c>
       <c r="AG6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI6" t="s">
         <v>228</v>
       </c>
       <c r="AJ6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK6">
         <v>39.0979</v>
@@ -4417,16 +4423,16 @@
         <v>45</v>
       </c>
       <c r="AO6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AR6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AS6">
         <v>1</v>
@@ -4504,7 +4510,7 @@
         <v>9.9</v>
       </c>
       <c r="BR6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BS6">
         <v>3.1</v>
@@ -4546,7 +4552,7 @@
         <v>29.1</v>
       </c>
       <c r="CF6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG6">
         <v>84</v>
@@ -4573,7 +4579,7 @@
         <v>8.4</v>
       </c>
       <c r="CO6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CP6">
         <v>1.9</v>
@@ -4615,7 +4621,7 @@
         <v>26.6</v>
       </c>
       <c r="DC6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD6">
         <v>81.3</v>
@@ -4642,7 +4648,7 @@
         <v>6.1</v>
       </c>
       <c r="DL6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="DM6">
         <v>1.7</v>
@@ -4684,7 +4690,7 @@
         <v>23.4</v>
       </c>
       <c r="DZ6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EA6">
         <v>78.59999999999999</v>
@@ -4711,7 +4717,7 @@
         <v>7.4</v>
       </c>
       <c r="EI6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="EJ6">
         <v>1.1</v>
@@ -4753,7 +4759,7 @@
         <v>24</v>
       </c>
       <c r="EW6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EX6">
         <v>93</v>
@@ -4824,10 +4830,10 @@
         <v>1.017</v>
       </c>
       <c r="V7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="W7">
-        <v>141.5</v>
+        <v>142.3</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -4845,28 +4851,28 @@
         <v>858</v>
       </c>
       <c r="AC7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF7">
         <v>30.2</v>
       </c>
       <c r="AG7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AH7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AI7" t="s">
         <v>229</v>
       </c>
       <c r="AJ7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK7">
         <v>27.7683</v>
@@ -4881,16 +4887,16 @@
         <v>45</v>
       </c>
       <c r="AO7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AR7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AS7">
         <v>0.92</v>
@@ -4968,7 +4974,7 @@
         <v>9.5</v>
       </c>
       <c r="BR7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="BS7">
         <v>0</v>
@@ -5010,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="CF7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CG7">
         <v>84.8</v>
@@ -5037,7 +5043,7 @@
         <v>15.5</v>
       </c>
       <c r="CO7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="CP7">
         <v>0</v>
@@ -5079,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="DC7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="DD7">
         <v>83.90000000000001</v>
@@ -5106,7 +5112,7 @@
         <v>7.5</v>
       </c>
       <c r="DL7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="DM7">
         <v>0</v>
@@ -5148,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="EA7">
         <v>83.5</v>
@@ -5175,7 +5181,7 @@
         <v>9.1</v>
       </c>
       <c r="EI7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="EJ7">
         <v>0</v>
@@ -5217,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="EW7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="EX7">
         <v>27</v>
@@ -5288,10 +5294,10 @@
         <v>1.028</v>
       </c>
       <c r="V8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W8">
-        <v>36.2</v>
+        <v>37</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -5309,28 +5315,28 @@
         <v>1445</v>
       </c>
       <c r="AC8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AD8">
         <v>26.6</v>
       </c>
       <c r="AE8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF8">
         <v>18.6</v>
       </c>
       <c r="AG8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AI8" t="s">
         <v>230</v>
       </c>
       <c r="AJ8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK8">
         <v>25.7781</v>
@@ -5345,16 +5351,16 @@
         <v>45</v>
       </c>
       <c r="AO8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AR8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AS8">
         <v>0.92</v>
@@ -5432,7 +5438,7 @@
         <v>12.9</v>
       </c>
       <c r="BR8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="BS8">
         <v>-5.1</v>
@@ -5474,7 +5480,7 @@
         <v>26.6</v>
       </c>
       <c r="CF8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG8">
         <v>83</v>
@@ -5501,7 +5507,7 @@
         <v>10.6</v>
       </c>
       <c r="CO8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CP8">
         <v>-4.5</v>
@@ -5543,7 +5549,7 @@
         <v>24.1</v>
       </c>
       <c r="DC8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD8">
         <v>82.5</v>
@@ -5570,7 +5576,7 @@
         <v>10.1</v>
       </c>
       <c r="DL8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="DM8">
         <v>0</v>
@@ -5612,7 +5618,7 @@
         <v>24</v>
       </c>
       <c r="DZ8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EA8">
         <v>81.90000000000001</v>
@@ -5639,7 +5645,7 @@
         <v>11.5</v>
       </c>
       <c r="EI8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="EJ8">
         <v>-3.9</v>
@@ -5681,7 +5687,7 @@
         <v>24.9</v>
       </c>
       <c r="EW8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EX8">
         <v>40</v>
@@ -5752,10 +5758,10 @@
         <v>1.031</v>
       </c>
       <c r="V9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="W9">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -5773,28 +5779,28 @@
         <v>1669</v>
       </c>
       <c r="AC9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AD9">
         <v>25.2</v>
       </c>
       <c r="AE9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF9">
         <v>11.6</v>
       </c>
       <c r="AG9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI9" t="s">
         <v>231</v>
       </c>
       <c r="AJ9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK9">
         <v>40.7571</v>
@@ -5809,16 +5815,16 @@
         <v>20</v>
       </c>
       <c r="AO9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AR9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AS9">
         <v>0.92</v>
@@ -5896,7 +5902,7 @@
         <v>11.2</v>
       </c>
       <c r="BR9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="BS9">
         <v>-2.8</v>
@@ -5938,7 +5944,7 @@
         <v>23.9</v>
       </c>
       <c r="CF9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG9">
         <v>81.90000000000001</v>
@@ -5965,7 +5971,7 @@
         <v>10.5</v>
       </c>
       <c r="CO9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="CP9">
         <v>-2.2</v>
@@ -6007,7 +6013,7 @@
         <v>24.4</v>
       </c>
       <c r="DC9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD9">
         <v>79.09999999999999</v>
@@ -6034,7 +6040,7 @@
         <v>8.4</v>
       </c>
       <c r="DL9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="DM9">
         <v>-1.9</v>
@@ -6076,7 +6082,7 @@
         <v>25.2</v>
       </c>
       <c r="DZ9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EA9">
         <v>77.90000000000001</v>
@@ -6103,7 +6109,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="EI9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="EJ9">
         <v>-4.1</v>
@@ -6145,7 +6151,7 @@
         <v>25.2</v>
       </c>
       <c r="EW9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="EX9">
         <v>53</v>
@@ -6219,7 +6225,7 @@
         <v>284</v>
       </c>
       <c r="W10">
-        <v>91.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -6237,28 +6243,28 @@
         <v>1611</v>
       </c>
       <c r="AC10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AD10">
         <v>2.1</v>
       </c>
       <c r="AE10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF10">
         <v>8.699999999999999</v>
       </c>
       <c r="AG10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI10" t="s">
         <v>232</v>
       </c>
       <c r="AJ10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK10">
         <v>41.83</v>
@@ -6273,16 +6279,16 @@
         <v>30</v>
       </c>
       <c r="AO10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AR10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AS10">
         <v>0.92</v>
@@ -6360,7 +6366,7 @@
         <v>13.4</v>
       </c>
       <c r="BR10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="BS10">
         <v>-7.7</v>
@@ -6402,7 +6408,7 @@
         <v>2.1</v>
       </c>
       <c r="CF10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CG10">
         <v>72.40000000000001</v>
@@ -6429,7 +6435,7 @@
         <v>14.3</v>
       </c>
       <c r="CO10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CP10">
         <v>-8</v>
@@ -6471,7 +6477,7 @@
         <v>2</v>
       </c>
       <c r="DC10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD10">
         <v>71.8</v>
@@ -6498,7 +6504,7 @@
         <v>12.2</v>
       </c>
       <c r="DL10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="DM10">
         <v>-7.5</v>
@@ -6540,7 +6546,7 @@
         <v>0.7</v>
       </c>
       <c r="DZ10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA10">
         <v>71.09999999999999</v>
@@ -6567,7 +6573,7 @@
         <v>11.2</v>
       </c>
       <c r="EI10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="EJ10">
         <v>-5.5</v>
@@ -6609,7 +6615,7 @@
         <v>0.7</v>
       </c>
       <c r="EW10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX10">
         <v>13</v>
@@ -6683,7 +6689,7 @@
         <v>285</v>
       </c>
       <c r="W11">
-        <v>176.9</v>
+        <v>177.7</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -6701,28 +6707,28 @@
         <v>858</v>
       </c>
       <c r="AC11" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
         <v>293</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>292</v>
       </c>
       <c r="AF11">
         <v>14.2</v>
       </c>
       <c r="AG11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AH11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AI11" t="s">
         <v>233</v>
       </c>
       <c r="AJ11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK11">
         <v>32.7473</v>
@@ -6737,16 +6743,16 @@
         <v>45</v>
       </c>
       <c r="AO11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AR11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AS11">
         <v>0.92</v>
@@ -6824,7 +6830,7 @@
         <v>20.9</v>
       </c>
       <c r="BR11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BS11">
         <v>0</v>
@@ -6866,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="CF11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CG11">
         <v>94.3</v>
@@ -6893,7 +6899,7 @@
         <v>20</v>
       </c>
       <c r="CO11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CP11">
         <v>0</v>
@@ -6935,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="DC11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="DD11">
         <v>91.40000000000001</v>
@@ -6962,7 +6968,7 @@
         <v>20.1</v>
       </c>
       <c r="DL11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="DM11">
         <v>0</v>
@@ -7004,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="DZ11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="EA11">
         <v>89.09999999999999</v>
@@ -7031,7 +7037,7 @@
         <v>20.3</v>
       </c>
       <c r="EI11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="EJ11">
         <v>0</v>
@@ -7073,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="EW11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="EX11">
         <v>33</v>
@@ -7147,7 +7153,7 @@
         <v>286</v>
       </c>
       <c r="W12">
-        <v>131.6</v>
+        <v>132.4</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -7165,28 +7171,28 @@
         <v>2673</v>
       </c>
       <c r="AC12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AD12">
         <v>7.6</v>
       </c>
       <c r="AE12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF12">
         <v>6.3</v>
       </c>
       <c r="AG12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI12" t="s">
         <v>234</v>
       </c>
       <c r="AJ12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK12">
         <v>44.9817</v>
@@ -7201,16 +7207,16 @@
         <v>45</v>
       </c>
       <c r="AO12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AS12">
         <v>0.92</v>
@@ -7288,7 +7294,7 @@
         <v>6.6</v>
       </c>
       <c r="BR12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BS12">
         <v>2.4</v>
@@ -7330,7 +7336,7 @@
         <v>7.6</v>
       </c>
       <c r="CF12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CG12">
         <v>84.90000000000001</v>
@@ -7357,7 +7363,7 @@
         <v>4.8</v>
       </c>
       <c r="CO12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CP12">
         <v>2.2</v>
@@ -7399,7 +7405,7 @@
         <v>6.4</v>
       </c>
       <c r="DC12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD12">
         <v>81.8</v>
@@ -7426,7 +7432,7 @@
         <v>4.1</v>
       </c>
       <c r="DL12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="DM12">
         <v>1.4</v>
@@ -7468,7 +7474,7 @@
         <v>7.4</v>
       </c>
       <c r="DZ12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA12">
         <v>79</v>
@@ -7495,7 +7501,7 @@
         <v>3</v>
       </c>
       <c r="EI12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="EJ12">
         <v>-0.3</v>
@@ -7537,7 +7543,7 @@
         <v>5.3</v>
       </c>
       <c r="EW12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX12">
         <v>100</v>
@@ -7611,7 +7617,7 @@
         <v>287</v>
       </c>
       <c r="W13">
-        <v>91.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -7629,28 +7635,28 @@
         <v>2064</v>
       </c>
       <c r="AC13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AD13">
         <v>66</v>
       </c>
       <c r="AE13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF13">
         <v>25.5</v>
       </c>
       <c r="AG13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI13" t="s">
         <v>235</v>
       </c>
       <c r="AJ13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK13">
         <v>38.6226</v>
@@ -7665,16 +7671,16 @@
         <v>40</v>
       </c>
       <c r="AO13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AS13">
         <v>0.92</v>
@@ -7752,7 +7758,7 @@
         <v>10.7</v>
       </c>
       <c r="BR13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BS13">
         <v>3.3</v>
@@ -7794,7 +7800,7 @@
         <v>58</v>
       </c>
       <c r="CF13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="CG13">
         <v>81.09999999999999</v>
@@ -7821,7 +7827,7 @@
         <v>12.3</v>
       </c>
       <c r="CO13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CP13">
         <v>-2.4</v>
@@ -7863,7 +7869,7 @@
         <v>40.4</v>
       </c>
       <c r="DC13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD13">
         <v>78.40000000000001</v>
@@ -7890,7 +7896,7 @@
         <v>12.3</v>
       </c>
       <c r="DL13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="DM13">
         <v>2.3</v>
@@ -7932,7 +7938,7 @@
         <v>45.9</v>
       </c>
       <c r="DZ13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="EA13">
         <v>76.7</v>
@@ -7959,7 +7965,7 @@
         <v>14.6</v>
       </c>
       <c r="EI13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="EJ13">
         <v>0.4</v>
@@ -8001,7 +8007,7 @@
         <v>66</v>
       </c>
       <c r="EW13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="EX13">
         <v>60</v>
@@ -8075,7 +8081,7 @@
         <v>288</v>
       </c>
       <c r="W14">
-        <v>88.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -8093,28 +8099,28 @@
         <v>579</v>
       </c>
       <c r="AC14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AD14">
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF14">
         <v>7.4</v>
       </c>
       <c r="AG14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI14" t="s">
         <v>236</v>
       </c>
       <c r="AJ14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AK14">
         <v>32.7073</v>
@@ -8129,16 +8135,16 @@
         <v>35</v>
       </c>
       <c r="AO14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AR14" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AS14">
         <v>0.86</v>
@@ -8216,7 +8222,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="BR14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BS14">
         <v>4.6</v>
@@ -8258,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="CF14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CG14">
         <v>64.2</v>
@@ -8285,7 +8291,7 @@
         <v>8</v>
       </c>
       <c r="CO14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="CP14">
         <v>4.1</v>
@@ -8327,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="DC14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD14">
         <v>63.9</v>
@@ -8354,7 +8360,7 @@
         <v>7</v>
       </c>
       <c r="DL14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="DM14">
         <v>3.2</v>
@@ -8396,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="DZ14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA14">
         <v>63.4</v>
@@ -8423,7 +8429,7 @@
         <v>5.9</v>
       </c>
       <c r="EI14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="EJ14">
         <v>2.8</v>
@@ -8465,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="EW14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX14">
         <v>20</v>
@@ -8539,7 +8545,7 @@
         <v>289</v>
       </c>
       <c r="W15">
-        <v>105.7</v>
+        <v>106.5</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -8557,28 +8563,28 @@
         <v>1784</v>
       </c>
       <c r="AC15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AD15">
         <v>0</v>
       </c>
       <c r="AE15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF15">
         <v>13.2</v>
       </c>
       <c r="AG15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AK15">
         <v>34.0739</v>
@@ -8593,16 +8599,16 @@
         <v>35</v>
       </c>
       <c r="AO15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AR15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AS15">
         <v>0.78</v>
@@ -8680,7 +8686,7 @@
         <v>7.8</v>
       </c>
       <c r="BR15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="BS15">
         <v>5.5</v>
@@ -8722,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="CF15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CG15">
         <v>74.59999999999999</v>
@@ -8749,7 +8755,7 @@
         <v>6.7</v>
       </c>
       <c r="CO15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CP15">
         <v>3.6</v>
@@ -8791,7 +8797,7 @@
         <v>0</v>
       </c>
       <c r="DC15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD15">
         <v>71.40000000000001</v>
@@ -8818,7 +8824,7 @@
         <v>5.8</v>
       </c>
       <c r="DL15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="DM15">
         <v>3.4</v>
@@ -8860,7 +8866,7 @@
         <v>0</v>
       </c>
       <c r="DZ15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA15">
         <v>70.2</v>
@@ -8887,7 +8893,7 @@
         <v>4.5</v>
       </c>
       <c r="EI15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="EJ15">
         <v>3</v>
@@ -8929,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="EW15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX15">
         <v>87</v>
@@ -9000,10 +9006,10 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="W16">
-        <v>57.5</v>
+        <v>58.3</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -9021,28 +9027,28 @@
         <v>-191</v>
       </c>
       <c r="AC16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AD16">
         <v>0.4</v>
       </c>
       <c r="AE16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF16">
         <v>11.7</v>
       </c>
       <c r="AG16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI16" t="s">
         <v>238</v>
       </c>
       <c r="AJ16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AK16">
         <v>37.7786</v>
@@ -9057,16 +9063,16 @@
         <v>45</v>
       </c>
       <c r="AO16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ16" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AR16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AS16">
         <v>0.82</v>
@@ -9144,7 +9150,7 @@
         <v>19.5</v>
       </c>
       <c r="BR16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BS16">
         <v>6.3</v>
@@ -9186,7 +9192,7 @@
         <v>0.4</v>
       </c>
       <c r="CF16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CG16">
         <v>55.7</v>
@@ -9213,7 +9219,7 @@
         <v>18.9</v>
       </c>
       <c r="CO16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CP16">
         <v>6.7</v>
@@ -9255,7 +9261,7 @@
         <v>0.4</v>
       </c>
       <c r="DC16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD16">
         <v>54.9</v>
@@ -9282,7 +9288,7 @@
         <v>17.8</v>
       </c>
       <c r="DL16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="DM16">
         <v>8.199999999999999</v>
@@ -9324,7 +9330,7 @@
         <v>0.4</v>
       </c>
       <c r="DZ16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EA16">
         <v>54.6</v>
@@ -9351,7 +9357,7 @@
         <v>16</v>
       </c>
       <c r="EI16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="EJ16">
         <v>7.2</v>
@@ -9393,7 +9399,7 @@
         <v>0.4</v>
       </c>
       <c r="EW16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="EX16">
         <v>7</v>
@@ -9507,10 +9513,10 @@
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>42</v>
@@ -9525,28 +9531,28 @@
         <v>22</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>44</v>
@@ -9558,109 +9564,109 @@
         <v>46</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="BE1" s="3" t="s">
         <v>31</v>
@@ -9669,16 +9675,16 @@
         <v>30</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:62">
@@ -9695,22 +9701,22 @@
         <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F2" t="s">
         <v>212</v>
       </c>
       <c r="G2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H2" t="s">
         <v>277</v>
       </c>
       <c r="I2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J2">
-        <v>58.2</v>
+        <v>59</v>
       </c>
       <c r="K2">
         <v>1.3</v>
@@ -9749,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X2">
         <v>81</v>
@@ -9791,7 +9797,7 @@
         <v>7.1</v>
       </c>
       <c r="AK2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL2">
         <v>67.5</v>
@@ -9812,16 +9818,16 @@
         <v>1.1386</v>
       </c>
       <c r="AR2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS2">
         <v>2227</v>
       </c>
       <c r="AT2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV2">
         <v>65.59999999999999</v>
@@ -9848,13 +9854,13 @@
         <v>23.2</v>
       </c>
       <c r="BD2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE2">
         <v>6.4</v>
       </c>
       <c r="BF2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG2">
         <v>81</v>
@@ -9883,22 +9889,22 @@
         <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H3" t="s">
         <v>277</v>
       </c>
       <c r="I3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J3">
-        <v>58.2</v>
+        <v>59</v>
       </c>
       <c r="K3">
         <v>2.3</v>
@@ -9937,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X3">
         <v>78.7</v>
@@ -9979,7 +9985,7 @@
         <v>7.4</v>
       </c>
       <c r="AK3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL3">
         <v>67.5</v>
@@ -10000,16 +10006,16 @@
         <v>1.1436</v>
       </c>
       <c r="AR3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS3">
         <v>2069</v>
       </c>
       <c r="AT3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV3">
         <v>62.6</v>
@@ -10036,13 +10042,13 @@
         <v>21.9</v>
       </c>
       <c r="BD3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE3">
         <v>4.2</v>
       </c>
       <c r="BF3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG3">
         <v>79</v>
@@ -10071,22 +10077,22 @@
         <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H4" t="s">
         <v>277</v>
       </c>
       <c r="I4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J4">
-        <v>58.2</v>
+        <v>59</v>
       </c>
       <c r="K4">
         <v>3.3</v>
@@ -10125,7 +10131,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X4">
         <v>76.59999999999999</v>
@@ -10167,7 +10173,7 @@
         <v>9.1</v>
       </c>
       <c r="AK4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL4">
         <v>45</v>
@@ -10188,16 +10194,16 @@
         <v>1.1483</v>
       </c>
       <c r="AR4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS4">
         <v>1924</v>
       </c>
       <c r="AT4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV4">
         <v>60.2</v>
@@ -10224,13 +10230,13 @@
         <v>19.1</v>
       </c>
       <c r="BD4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE4">
         <v>3.7</v>
       </c>
       <c r="BF4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG4">
         <v>77</v>
@@ -10259,22 +10265,22 @@
         <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H5" t="s">
         <v>277</v>
       </c>
       <c r="I5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J5">
-        <v>58.2</v>
+        <v>59</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -10313,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="X5">
         <v>74.09999999999999</v>
@@ -10355,7 +10361,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL5">
         <v>45</v>
@@ -10376,16 +10382,16 @@
         <v>1.1542</v>
       </c>
       <c r="AR5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS5">
         <v>1744</v>
       </c>
       <c r="AT5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV5">
         <v>58.7</v>
@@ -10412,13 +10418,13 @@
         <v>27.5</v>
       </c>
       <c r="BD5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE5">
         <v>4.7</v>
       </c>
       <c r="BF5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG5">
         <v>74</v>
@@ -10447,22 +10453,22 @@
         <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F6" t="s">
         <v>212</v>
       </c>
       <c r="G6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H6" t="s">
         <v>278</v>
       </c>
       <c r="I6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J6">
-        <v>181.6</v>
+        <v>182.4</v>
       </c>
       <c r="K6">
         <v>1.3</v>
@@ -10501,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X6">
         <v>76.8</v>
@@ -10543,7 +10549,7 @@
         <v>5.9</v>
       </c>
       <c r="AK6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL6">
         <v>225</v>
@@ -10564,16 +10570,16 @@
         <v>1.1353</v>
       </c>
       <c r="AR6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS6">
         <v>2272</v>
       </c>
       <c r="AT6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV6">
         <v>72.2</v>
@@ -10600,13 +10606,13 @@
         <v>46.3</v>
       </c>
       <c r="BD6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BE6">
         <v>20.7</v>
       </c>
       <c r="BF6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG6">
         <v>79</v>
@@ -10635,22 +10641,22 @@
         <v>225</v>
       </c>
       <c r="E7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H7" t="s">
         <v>278</v>
       </c>
       <c r="I7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J7">
-        <v>181.6</v>
+        <v>182.4</v>
       </c>
       <c r="K7">
         <v>2.3</v>
@@ -10689,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="X7">
         <v>75.59999999999999</v>
@@ -10731,7 +10737,7 @@
         <v>10.1</v>
       </c>
       <c r="AK7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL7">
         <v>225</v>
@@ -10752,16 +10758,16 @@
         <v>1.1382</v>
       </c>
       <c r="AR7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS7">
         <v>2186</v>
       </c>
       <c r="AT7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV7">
         <v>71.09999999999999</v>
@@ -10788,13 +10794,13 @@
         <v>44.9</v>
       </c>
       <c r="BD7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE7">
         <v>17.3</v>
       </c>
       <c r="BF7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG7">
         <v>77</v>
@@ -10823,22 +10829,22 @@
         <v>225</v>
       </c>
       <c r="E8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H8" t="s">
         <v>278</v>
       </c>
       <c r="I8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J8">
-        <v>181.6</v>
+        <v>182.4</v>
       </c>
       <c r="K8">
         <v>3.3</v>
@@ -10877,7 +10883,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="X8">
         <v>73.90000000000001</v>
@@ -10919,7 +10925,7 @@
         <v>5.1</v>
       </c>
       <c r="AK8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL8">
         <v>180</v>
@@ -10940,16 +10946,16 @@
         <v>1.142</v>
       </c>
       <c r="AR8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS8">
         <v>2074</v>
       </c>
       <c r="AT8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV8">
         <v>67.5</v>
@@ -10976,13 +10982,13 @@
         <v>38.4</v>
       </c>
       <c r="BD8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE8">
         <v>15.1</v>
       </c>
       <c r="BF8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG8">
         <v>75</v>
@@ -11011,22 +11017,22 @@
         <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H9" t="s">
         <v>278</v>
       </c>
       <c r="I9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J9">
-        <v>181.6</v>
+        <v>182.4</v>
       </c>
       <c r="K9">
         <v>4.3</v>
@@ -11065,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="X9">
         <v>73.09999999999999</v>
@@ -11107,7 +11113,7 @@
         <v>3.4</v>
       </c>
       <c r="AK9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL9">
         <v>270</v>
@@ -11128,16 +11134,16 @@
         <v>1.144</v>
       </c>
       <c r="AR9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS9">
         <v>2014</v>
       </c>
       <c r="AT9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV9">
         <v>66.90000000000001</v>
@@ -11164,13 +11170,13 @@
         <v>27.1</v>
       </c>
       <c r="BD9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE9">
         <v>12.6</v>
       </c>
       <c r="BF9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG9">
         <v>74</v>
@@ -11199,25 +11205,25 @@
         <v>226</v>
       </c>
       <c r="E10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F10" t="s">
         <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H10" t="s">
         <v>279</v>
       </c>
       <c r="I10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J10">
-        <v>30.1</v>
+        <v>30.9</v>
       </c>
       <c r="K10">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -11253,7 +11259,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X10">
         <v>82.5</v>
@@ -11295,7 +11301,7 @@
         <v>7.8</v>
       </c>
       <c r="AK10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL10">
         <v>270</v>
@@ -11316,16 +11322,16 @@
         <v>1.155</v>
       </c>
       <c r="AR10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS10">
         <v>1721</v>
       </c>
       <c r="AT10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV10">
         <v>69.5</v>
@@ -11352,13 +11358,13 @@
         <v>14.9</v>
       </c>
       <c r="BD10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE10">
         <v>11.7</v>
       </c>
       <c r="BF10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG10">
         <v>84</v>
@@ -11387,25 +11393,25 @@
         <v>226</v>
       </c>
       <c r="E11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H11" t="s">
         <v>279</v>
       </c>
       <c r="I11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J11">
-        <v>30.1</v>
+        <v>30.9</v>
       </c>
       <c r="K11">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -11441,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X11">
         <v>81.09999999999999</v>
@@ -11483,7 +11489,7 @@
         <v>5.9</v>
       </c>
       <c r="AK11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL11">
         <v>270</v>
@@ -11504,16 +11510,16 @@
         <v>1.1585</v>
       </c>
       <c r="AR11" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS11">
         <v>1617</v>
       </c>
       <c r="AT11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV11">
         <v>68.09999999999999</v>
@@ -11540,13 +11546,13 @@
         <v>12.1</v>
       </c>
       <c r="BD11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE11">
         <v>8</v>
       </c>
       <c r="BF11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG11">
         <v>82</v>
@@ -11575,25 +11581,25 @@
         <v>226</v>
       </c>
       <c r="E12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H12" t="s">
         <v>279</v>
       </c>
       <c r="I12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J12">
-        <v>30.1</v>
+        <v>30.9</v>
       </c>
       <c r="K12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -11629,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X12">
         <v>78.90000000000001</v>
@@ -11671,7 +11677,7 @@
         <v>5.4</v>
       </c>
       <c r="AK12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL12">
         <v>180</v>
@@ -11692,16 +11698,16 @@
         <v>1.163</v>
       </c>
       <c r="AR12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS12">
         <v>1480</v>
       </c>
       <c r="AT12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV12">
         <v>67.90000000000001</v>
@@ -11728,13 +11734,13 @@
         <v>8.9</v>
       </c>
       <c r="BD12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE12">
         <v>7.9</v>
       </c>
       <c r="BF12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG12">
         <v>80</v>
@@ -11763,25 +11769,25 @@
         <v>226</v>
       </c>
       <c r="E13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F13" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H13" t="s">
         <v>279</v>
       </c>
       <c r="I13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J13">
-        <v>30.1</v>
+        <v>30.9</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -11817,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X13">
         <v>77.3</v>
@@ -11859,7 +11865,7 @@
         <v>4.5</v>
       </c>
       <c r="AK13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL13">
         <v>224.6</v>
@@ -11880,16 +11886,16 @@
         <v>1.1664</v>
       </c>
       <c r="AR13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS13">
         <v>1367</v>
       </c>
       <c r="AT13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV13">
         <v>66.09999999999999</v>
@@ -11916,13 +11922,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE13">
         <v>2.8</v>
       </c>
       <c r="BF13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG13">
         <v>78</v>
@@ -11951,22 +11957,22 @@
         <v>227</v>
       </c>
       <c r="E14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F14" t="s">
         <v>214</v>
       </c>
       <c r="G14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H14" t="s">
         <v>280</v>
       </c>
       <c r="I14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J14">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="K14">
         <v>1.7</v>
@@ -12005,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X14">
         <v>81.09999999999999</v>
@@ -12047,7 +12053,7 @@
         <v>12.3</v>
       </c>
       <c r="AK14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL14">
         <v>270</v>
@@ -12068,16 +12074,16 @@
         <v>1.1599</v>
       </c>
       <c r="AR14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS14">
         <v>1559</v>
       </c>
       <c r="AT14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV14">
         <v>70.09999999999999</v>
@@ -12104,13 +12110,13 @@
         <v>20.9</v>
       </c>
       <c r="BD14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE14">
         <v>7</v>
       </c>
       <c r="BF14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG14">
         <v>83</v>
@@ -12139,22 +12145,22 @@
         <v>227</v>
       </c>
       <c r="E15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H15" t="s">
         <v>280</v>
       </c>
       <c r="I15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J15">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="K15">
         <v>2.7</v>
@@ -12193,7 +12199,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X15">
         <v>78.90000000000001</v>
@@ -12235,7 +12241,7 @@
         <v>8.5</v>
       </c>
       <c r="AK15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL15">
         <v>270</v>
@@ -12256,16 +12262,16 @@
         <v>1.1648</v>
       </c>
       <c r="AR15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS15">
         <v>1415</v>
       </c>
       <c r="AT15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV15">
         <v>67.5</v>
@@ -12292,13 +12298,13 @@
         <v>15.5</v>
       </c>
       <c r="BD15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE15">
         <v>10.3</v>
       </c>
       <c r="BF15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG15">
         <v>81</v>
@@ -12327,22 +12333,22 @@
         <v>227</v>
       </c>
       <c r="E16" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F16" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H16" t="s">
         <v>280</v>
       </c>
       <c r="I16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J16">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="K16">
         <v>3.7</v>
@@ -12381,7 +12387,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X16">
         <v>77.2</v>
@@ -12423,7 +12429,7 @@
         <v>7</v>
       </c>
       <c r="AK16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL16">
         <v>270</v>
@@ -12444,16 +12450,16 @@
         <v>1.1681</v>
       </c>
       <c r="AR16" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS16">
         <v>1306</v>
       </c>
       <c r="AT16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV16">
         <v>66</v>
@@ -12480,13 +12486,13 @@
         <v>11.2</v>
       </c>
       <c r="BD16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE16">
         <v>10.7</v>
       </c>
       <c r="BF16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG16">
         <v>79</v>
@@ -12515,22 +12521,22 @@
         <v>227</v>
       </c>
       <c r="E17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F17" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H17" t="s">
         <v>280</v>
       </c>
       <c r="I17" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J17">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="K17">
         <v>4.7</v>
@@ -12569,7 +12575,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X17">
         <v>75.8</v>
@@ -12611,7 +12617,7 @@
         <v>4.6</v>
       </c>
       <c r="AK17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL17">
         <v>255.2</v>
@@ -12632,16 +12638,16 @@
         <v>1.1716</v>
       </c>
       <c r="AR17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS17">
         <v>1204</v>
       </c>
       <c r="AT17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV17">
         <v>63.8</v>
@@ -12668,13 +12674,13 @@
         <v>9</v>
       </c>
       <c r="BD17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE17">
         <v>4.7</v>
       </c>
       <c r="BF17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG17">
         <v>77</v>
@@ -12703,22 +12709,22 @@
         <v>228</v>
       </c>
       <c r="E18" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F18" t="s">
         <v>215</v>
       </c>
       <c r="G18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H18" t="s">
         <v>281</v>
       </c>
       <c r="I18" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J18">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="K18">
         <v>1.8</v>
@@ -12757,7 +12763,7 @@
         <v>2.2</v>
       </c>
       <c r="W18" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X18">
         <v>85</v>
@@ -12799,7 +12805,7 @@
         <v>9.9</v>
       </c>
       <c r="AK18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL18">
         <v>270</v>
@@ -12820,16 +12826,16 @@
         <v>1.1281</v>
       </c>
       <c r="AR18" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS18">
         <v>2523</v>
       </c>
       <c r="AT18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV18">
         <v>79</v>
@@ -12856,13 +12862,13 @@
         <v>29.1</v>
       </c>
       <c r="BD18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE18">
         <v>10.5</v>
       </c>
       <c r="BF18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG18">
         <v>84</v>
@@ -12891,22 +12897,22 @@
         <v>228</v>
       </c>
       <c r="E19" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F19" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H19" t="s">
         <v>281</v>
       </c>
       <c r="I19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J19">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="K19">
         <v>2.8</v>
@@ -12945,7 +12951,7 @@
         <v>2.2</v>
       </c>
       <c r="W19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X19">
         <v>84</v>
@@ -12987,7 +12993,7 @@
         <v>8.4</v>
       </c>
       <c r="AK19" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL19">
         <v>270</v>
@@ -13008,16 +13014,16 @@
         <v>1.1302</v>
       </c>
       <c r="AR19" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS19">
         <v>2449</v>
       </c>
       <c r="AT19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV19">
         <v>76.8</v>
@@ -13044,13 +13050,13 @@
         <v>26.6</v>
       </c>
       <c r="BD19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE19">
         <v>9.300000000000001</v>
       </c>
       <c r="BF19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG19">
         <v>83</v>
@@ -13079,22 +13085,22 @@
         <v>228</v>
       </c>
       <c r="E20" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F20" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H20" t="s">
         <v>281</v>
       </c>
       <c r="I20" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J20">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="K20">
         <v>3.8</v>
@@ -13133,7 +13139,7 @@
         <v>2.2</v>
       </c>
       <c r="W20" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X20">
         <v>81.3</v>
@@ -13175,7 +13181,7 @@
         <v>6.1</v>
       </c>
       <c r="AK20" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL20">
         <v>270</v>
@@ -13196,16 +13202,16 @@
         <v>1.1362</v>
       </c>
       <c r="AR20" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS20">
         <v>2271</v>
       </c>
       <c r="AT20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU20" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV20">
         <v>74.40000000000001</v>
@@ -13232,13 +13238,13 @@
         <v>23.4</v>
       </c>
       <c r="BD20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE20">
         <v>3</v>
       </c>
       <c r="BF20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG20">
         <v>80</v>
@@ -13267,22 +13273,22 @@
         <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F21" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H21" t="s">
         <v>281</v>
       </c>
       <c r="I21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J21">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="K21">
         <v>4.8</v>
@@ -13321,7 +13327,7 @@
         <v>2.2</v>
       </c>
       <c r="W21" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X21">
         <v>78.59999999999999</v>
@@ -13363,7 +13369,7 @@
         <v>7.4</v>
       </c>
       <c r="AK21" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL21">
         <v>270</v>
@@ -13384,16 +13390,16 @@
         <v>1.1421</v>
       </c>
       <c r="AR21" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS21">
         <v>2075</v>
       </c>
       <c r="AT21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV21">
         <v>71.59999999999999</v>
@@ -13420,13 +13426,13 @@
         <v>24</v>
       </c>
       <c r="BD21" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE21">
         <v>4.8</v>
       </c>
       <c r="BF21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG21">
         <v>77</v>
@@ -13455,22 +13461,22 @@
         <v>229</v>
       </c>
       <c r="E22" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F22" t="s">
         <v>215</v>
       </c>
       <c r="G22" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J22">
-        <v>141.5</v>
+        <v>142.3</v>
       </c>
       <c r="K22">
         <v>1.8</v>
@@ -13509,7 +13515,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="X22">
         <v>89.40000000000001</v>
@@ -13551,7 +13557,7 @@
         <v>9.5</v>
       </c>
       <c r="AK22" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL22">
         <v>157.5</v>
@@ -13572,16 +13578,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR22" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS22">
         <v>858</v>
       </c>
       <c r="AT22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AU22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AV22">
         <v>57</v>
@@ -13608,13 +13614,13 @@
         <v>0</v>
       </c>
       <c r="BD22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE22">
         <v>14.4</v>
       </c>
       <c r="BF22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG22">
         <v>91</v>
@@ -13643,22 +13649,22 @@
         <v>229</v>
       </c>
       <c r="E23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F23" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G23" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J23">
-        <v>141.5</v>
+        <v>142.3</v>
       </c>
       <c r="K23">
         <v>2.8</v>
@@ -13697,7 +13703,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="X23">
         <v>84.8</v>
@@ -13739,7 +13745,7 @@
         <v>15.5</v>
       </c>
       <c r="AK23" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL23">
         <v>157.5</v>
@@ -13760,16 +13766,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS23">
         <v>858</v>
       </c>
       <c r="AT23" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AU23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AV23">
         <v>57</v>
@@ -13796,13 +13802,13 @@
         <v>0</v>
       </c>
       <c r="BD23" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE23">
         <v>30.2</v>
       </c>
       <c r="BF23" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG23">
         <v>88</v>
@@ -13831,22 +13837,22 @@
         <v>229</v>
       </c>
       <c r="E24" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F24" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G24" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J24">
-        <v>141.5</v>
+        <v>142.3</v>
       </c>
       <c r="K24">
         <v>3.8</v>
@@ -13885,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X24">
         <v>83.90000000000001</v>
@@ -13927,7 +13933,7 @@
         <v>7.5</v>
       </c>
       <c r="AK24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL24">
         <v>180</v>
@@ -13948,16 +13954,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR24" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS24">
         <v>858</v>
       </c>
       <c r="AT24" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AU24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AV24">
         <v>57</v>
@@ -13984,13 +13990,13 @@
         <v>0</v>
       </c>
       <c r="BD24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE24">
         <v>17.9</v>
       </c>
       <c r="BF24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG24">
         <v>86</v>
@@ -14019,22 +14025,22 @@
         <v>229</v>
       </c>
       <c r="E25" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J25">
-        <v>141.5</v>
+        <v>142.3</v>
       </c>
       <c r="K25">
         <v>4.8</v>
@@ -14073,7 +14079,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X25">
         <v>83.5</v>
@@ -14115,7 +14121,7 @@
         <v>9.1</v>
       </c>
       <c r="AK25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AL25">
         <v>135</v>
@@ -14136,16 +14142,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR25" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS25">
         <v>858</v>
       </c>
       <c r="AT25" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AU25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AV25">
         <v>57</v>
@@ -14172,13 +14178,13 @@
         <v>0</v>
       </c>
       <c r="BD25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE25">
         <v>8.6</v>
       </c>
       <c r="BF25" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG25">
         <v>85</v>
@@ -14207,22 +14213,22 @@
         <v>230</v>
       </c>
       <c r="E26" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F26" t="s">
         <v>215</v>
       </c>
       <c r="G26" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I26" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J26">
-        <v>36.2</v>
+        <v>37</v>
       </c>
       <c r="K26">
         <v>1.8</v>
@@ -14261,7 +14267,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X26">
         <v>85.2</v>
@@ -14303,7 +14309,7 @@
         <v>12.9</v>
       </c>
       <c r="AK26" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL26">
         <v>90</v>
@@ -14324,16 +14330,16 @@
         <v>1.1586</v>
       </c>
       <c r="AR26" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS26">
         <v>1556</v>
       </c>
       <c r="AT26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AV26">
         <v>61.7</v>
@@ -14360,13 +14366,13 @@
         <v>26.6</v>
       </c>
       <c r="BD26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE26">
         <v>18.6</v>
       </c>
       <c r="BF26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG26">
         <v>87</v>
@@ -14395,22 +14401,22 @@
         <v>230</v>
       </c>
       <c r="E27" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F27" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J27">
-        <v>36.2</v>
+        <v>37</v>
       </c>
       <c r="K27">
         <v>2.8</v>
@@ -14449,7 +14455,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X27">
         <v>83</v>
@@ -14491,7 +14497,7 @@
         <v>10.6</v>
       </c>
       <c r="AK27" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL27">
         <v>90</v>
@@ -14512,16 +14518,16 @@
         <v>1.1643</v>
       </c>
       <c r="AR27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS27">
         <v>1398</v>
       </c>
       <c r="AT27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AV27">
         <v>60</v>
@@ -14548,13 +14554,13 @@
         <v>24.1</v>
       </c>
       <c r="BD27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE27">
         <v>7.5</v>
       </c>
       <c r="BF27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG27">
         <v>84</v>
@@ -14583,22 +14589,22 @@
         <v>230</v>
       </c>
       <c r="E28" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F28" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I28" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J28">
-        <v>36.2</v>
+        <v>37</v>
       </c>
       <c r="K28">
         <v>3.8</v>
@@ -14637,7 +14643,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X28">
         <v>82.5</v>
@@ -14679,7 +14685,7 @@
         <v>10.1</v>
       </c>
       <c r="AK28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AL28">
         <v>135</v>
@@ -14700,16 +14706,16 @@
         <v>1.1654</v>
       </c>
       <c r="AR28" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS28">
         <v>1355</v>
       </c>
       <c r="AT28" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AV28">
         <v>64.8</v>
@@ -14736,13 +14742,13 @@
         <v>24</v>
       </c>
       <c r="BD28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE28">
         <v>11.3</v>
       </c>
       <c r="BF28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG28">
         <v>84</v>
@@ -14771,22 +14777,22 @@
         <v>230</v>
       </c>
       <c r="E29" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F29" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G29" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I29" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J29">
-        <v>36.2</v>
+        <v>37</v>
       </c>
       <c r="K29">
         <v>4.8</v>
@@ -14825,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X29">
         <v>81.90000000000001</v>
@@ -14867,7 +14873,7 @@
         <v>11.5</v>
       </c>
       <c r="AK29" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL29">
         <v>90</v>
@@ -14888,16 +14894,16 @@
         <v>1.1668</v>
       </c>
       <c r="AR29" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS29">
         <v>1317</v>
       </c>
       <c r="AT29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AV29">
         <v>59.6</v>
@@ -14924,13 +14930,13 @@
         <v>24.9</v>
       </c>
       <c r="BD29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE29">
         <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG29">
         <v>83</v>
@@ -14959,25 +14965,25 @@
         <v>231</v>
       </c>
       <c r="E30" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F30" t="s">
         <v>216</v>
       </c>
       <c r="G30" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I30" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J30">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="K30">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -15013,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X30">
         <v>83.90000000000001</v>
@@ -15055,7 +15061,7 @@
         <v>11.2</v>
       </c>
       <c r="AK30" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL30">
         <v>315</v>
@@ -15076,16 +15082,16 @@
         <v>1.1527</v>
       </c>
       <c r="AR30" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS30">
         <v>1825</v>
       </c>
       <c r="AT30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV30">
         <v>64.2</v>
@@ -15112,13 +15118,13 @@
         <v>23.9</v>
       </c>
       <c r="BD30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE30">
         <v>11.6</v>
       </c>
       <c r="BF30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG30">
         <v>84</v>
@@ -15147,25 +15153,25 @@
         <v>231</v>
       </c>
       <c r="E31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H31" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I31" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J31">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="K31">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -15201,7 +15207,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X31">
         <v>81.90000000000001</v>
@@ -15243,7 +15249,7 @@
         <v>10.5</v>
       </c>
       <c r="AK31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL31">
         <v>315</v>
@@ -15264,16 +15270,16 @@
         <v>1.1569</v>
       </c>
       <c r="AR31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS31">
         <v>1678</v>
       </c>
       <c r="AT31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV31">
         <v>63.5</v>
@@ -15300,13 +15306,13 @@
         <v>24.4</v>
       </c>
       <c r="BD31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE31">
         <v>1.9</v>
       </c>
       <c r="BF31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG31">
         <v>82</v>
@@ -15335,25 +15341,25 @@
         <v>231</v>
       </c>
       <c r="E32" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F32" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G32" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I32" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J32">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="K32">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -15389,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X32">
         <v>79.09999999999999</v>
@@ -15431,7 +15437,7 @@
         <v>8.4</v>
       </c>
       <c r="AK32" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL32">
         <v>315</v>
@@ -15452,16 +15458,16 @@
         <v>1.1624</v>
       </c>
       <c r="AR32" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS32">
         <v>1486</v>
       </c>
       <c r="AT32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV32">
         <v>62</v>
@@ -15488,13 +15494,13 @@
         <v>25.2</v>
       </c>
       <c r="BD32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE32">
         <v>4.7</v>
       </c>
       <c r="BF32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG32">
         <v>79</v>
@@ -15523,25 +15529,25 @@
         <v>231</v>
       </c>
       <c r="E33" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F33" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G33" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I33" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J33">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="K33">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -15577,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X33">
         <v>77.90000000000001</v>
@@ -15619,7 +15625,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK33" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -15640,16 +15646,16 @@
         <v>1.1656</v>
       </c>
       <c r="AR33" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS33">
         <v>1387</v>
       </c>
       <c r="AT33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU33" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV33">
         <v>58.9</v>
@@ -15676,13 +15682,13 @@
         <v>25.2</v>
       </c>
       <c r="BD33" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE33">
         <v>5.2</v>
       </c>
       <c r="BF33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG33">
         <v>78</v>
@@ -15711,22 +15717,22 @@
         <v>232</v>
       </c>
       <c r="E34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F34" t="s">
         <v>217</v>
       </c>
       <c r="G34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H34" t="s">
         <v>284</v>
       </c>
       <c r="I34" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J34">
-        <v>91.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K34">
         <v>2.3</v>
@@ -15765,7 +15771,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X34">
         <v>73.8</v>
@@ -15807,7 +15813,7 @@
         <v>13.4</v>
       </c>
       <c r="AK34" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL34">
         <v>22.5</v>
@@ -15828,16 +15834,16 @@
         <v>1.1571</v>
       </c>
       <c r="AR34" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS34">
         <v>1690</v>
       </c>
       <c r="AT34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV34">
         <v>54.4</v>
@@ -15864,13 +15870,13 @@
         <v>2.1</v>
       </c>
       <c r="BD34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE34">
         <v>8.699999999999999</v>
       </c>
       <c r="BF34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG34">
         <v>73</v>
@@ -15899,22 +15905,22 @@
         <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F35" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H35" t="s">
         <v>284</v>
       </c>
       <c r="I35" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J35">
-        <v>91.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K35">
         <v>3.3</v>
@@ -15953,7 +15959,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X35">
         <v>72.40000000000001</v>
@@ -15995,7 +16001,7 @@
         <v>14.3</v>
       </c>
       <c r="AK35" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL35">
         <v>22.5</v>
@@ -16016,16 +16022,16 @@
         <v>1.1605</v>
       </c>
       <c r="AR35" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS35">
         <v>1595</v>
       </c>
       <c r="AT35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV35">
         <v>52.7</v>
@@ -16052,13 +16058,13 @@
         <v>2</v>
       </c>
       <c r="BD35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE35">
         <v>6.1</v>
       </c>
       <c r="BF35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG35">
         <v>72</v>
@@ -16087,22 +16093,22 @@
         <v>232</v>
       </c>
       <c r="E36" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F36" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G36" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H36" t="s">
         <v>284</v>
       </c>
       <c r="I36" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J36">
-        <v>91.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K36">
         <v>4.3</v>
@@ -16141,7 +16147,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X36">
         <v>71.8</v>
@@ -16183,7 +16189,7 @@
         <v>12.2</v>
       </c>
       <c r="AK36" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL36">
         <v>22.5</v>
@@ -16204,16 +16210,16 @@
         <v>1.1622</v>
       </c>
       <c r="AR36" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS36">
         <v>1543</v>
       </c>
       <c r="AT36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV36">
         <v>52.8</v>
@@ -16240,13 +16246,13 @@
         <v>0.7</v>
       </c>
       <c r="BD36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE36">
         <v>7.4</v>
       </c>
       <c r="BF36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG36">
         <v>72</v>
@@ -16275,22 +16281,22 @@
         <v>232</v>
       </c>
       <c r="E37" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F37" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H37" t="s">
         <v>284</v>
       </c>
       <c r="I37" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J37">
-        <v>91.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K37">
         <v>5.3</v>
@@ -16329,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X37">
         <v>71.09999999999999</v>
@@ -16371,7 +16377,7 @@
         <v>11.2</v>
       </c>
       <c r="AK37" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL37">
         <v>22.5</v>
@@ -16392,16 +16398,16 @@
         <v>1.1645</v>
       </c>
       <c r="AR37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS37">
         <v>1480</v>
       </c>
       <c r="AT37" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV37">
         <v>54.6</v>
@@ -16428,13 +16434,13 @@
         <v>0.7</v>
       </c>
       <c r="BD37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE37">
         <v>4.5</v>
       </c>
       <c r="BF37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG37">
         <v>71</v>
@@ -16463,22 +16469,22 @@
         <v>233</v>
       </c>
       <c r="E38" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F38" t="s">
         <v>218</v>
       </c>
       <c r="G38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H38" t="s">
         <v>285</v>
       </c>
       <c r="I38" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J38">
-        <v>176.9</v>
+        <v>177.7</v>
       </c>
       <c r="K38">
         <v>2.7</v>
@@ -16517,7 +16523,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X38">
         <v>96.40000000000001</v>
@@ -16559,7 +16565,7 @@
         <v>20.9</v>
       </c>
       <c r="AK38" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL38">
         <v>180</v>
@@ -16580,16 +16586,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS38">
         <v>858</v>
       </c>
       <c r="AT38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AU38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV38">
         <v>57</v>
@@ -16616,13 +16622,13 @@
         <v>0</v>
       </c>
       <c r="BD38" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE38">
         <v>11.2</v>
       </c>
       <c r="BF38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG38">
         <v>98</v>
@@ -16651,22 +16657,22 @@
         <v>233</v>
       </c>
       <c r="E39" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F39" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G39" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H39" t="s">
         <v>285</v>
       </c>
       <c r="I39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J39">
-        <v>176.9</v>
+        <v>177.7</v>
       </c>
       <c r="K39">
         <v>3.7</v>
@@ -16705,7 +16711,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X39">
         <v>94.3</v>
@@ -16747,7 +16753,7 @@
         <v>20</v>
       </c>
       <c r="AK39" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL39">
         <v>180</v>
@@ -16768,16 +16774,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR39" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS39">
         <v>858</v>
       </c>
       <c r="AT39" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AU39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV39">
         <v>57</v>
@@ -16804,13 +16810,13 @@
         <v>0</v>
       </c>
       <c r="BD39" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE39">
         <v>14.2</v>
       </c>
       <c r="BF39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG39">
         <v>96</v>
@@ -16839,22 +16845,22 @@
         <v>233</v>
       </c>
       <c r="E40" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F40" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H40" t="s">
         <v>285</v>
       </c>
       <c r="I40" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J40">
-        <v>176.9</v>
+        <v>177.7</v>
       </c>
       <c r="K40">
         <v>4.7</v>
@@ -16893,7 +16899,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X40">
         <v>91.40000000000001</v>
@@ -16935,7 +16941,7 @@
         <v>20.1</v>
       </c>
       <c r="AK40" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL40">
         <v>180</v>
@@ -16956,16 +16962,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR40" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS40">
         <v>858</v>
       </c>
       <c r="AT40" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AU40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV40">
         <v>57</v>
@@ -16992,13 +16998,13 @@
         <v>0</v>
       </c>
       <c r="BD40" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE40">
         <v>7.4</v>
       </c>
       <c r="BF40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG40">
         <v>93</v>
@@ -17027,22 +17033,22 @@
         <v>233</v>
       </c>
       <c r="E41" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F41" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G41" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H41" t="s">
         <v>285</v>
       </c>
       <c r="I41" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J41">
-        <v>176.9</v>
+        <v>177.7</v>
       </c>
       <c r="K41">
         <v>5.7</v>
@@ -17081,7 +17087,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X41">
         <v>89.09999999999999</v>
@@ -17123,7 +17129,7 @@
         <v>20.3</v>
       </c>
       <c r="AK41" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL41">
         <v>180</v>
@@ -17144,16 +17150,16 @@
         <v>1.1896</v>
       </c>
       <c r="AR41" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS41">
         <v>858</v>
       </c>
       <c r="AT41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AU41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AV41">
         <v>57</v>
@@ -17180,13 +17186,13 @@
         <v>0</v>
       </c>
       <c r="BD41" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BE41">
         <v>9</v>
       </c>
       <c r="BF41" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG41">
         <v>91</v>
@@ -17215,22 +17221,22 @@
         <v>234</v>
       </c>
       <c r="E42" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F42" t="s">
         <v>219</v>
       </c>
       <c r="G42" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H42" t="s">
         <v>286</v>
       </c>
       <c r="I42" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J42">
-        <v>131.6</v>
+        <v>132.4</v>
       </c>
       <c r="K42">
         <v>2.8</v>
@@ -17269,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X42">
         <v>86.2</v>
@@ -17311,7 +17317,7 @@
         <v>6.6</v>
       </c>
       <c r="AK42" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL42">
         <v>180</v>
@@ -17332,16 +17338,16 @@
         <v>1.1216</v>
       </c>
       <c r="AR42" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS42">
         <v>2811</v>
       </c>
       <c r="AT42" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU42" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV42">
         <v>78.8</v>
@@ -17368,13 +17374,13 @@
         <v>7.6</v>
       </c>
       <c r="BD42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE42">
         <v>5.8</v>
       </c>
       <c r="BF42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG42">
         <v>86</v>
@@ -17403,22 +17409,22 @@
         <v>234</v>
       </c>
       <c r="E43" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F43" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H43" t="s">
         <v>286</v>
       </c>
       <c r="I43" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J43">
-        <v>131.6</v>
+        <v>132.4</v>
       </c>
       <c r="K43">
         <v>3.8</v>
@@ -17457,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X43">
         <v>84.90000000000001</v>
@@ -17499,7 +17505,7 @@
         <v>4.8</v>
       </c>
       <c r="AK43" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL43">
         <v>180</v>
@@ -17520,16 +17526,16 @@
         <v>1.1242</v>
       </c>
       <c r="AR43" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS43">
         <v>2719</v>
       </c>
       <c r="AT43" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV43">
         <v>77.40000000000001</v>
@@ -17556,13 +17562,13 @@
         <v>6.4</v>
       </c>
       <c r="BD43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE43">
         <v>6.3</v>
       </c>
       <c r="BF43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG43">
         <v>85</v>
@@ -17591,22 +17597,22 @@
         <v>234</v>
       </c>
       <c r="E44" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F44" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G44" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H44" t="s">
         <v>286</v>
       </c>
       <c r="I44" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J44">
-        <v>131.6</v>
+        <v>132.4</v>
       </c>
       <c r="K44">
         <v>4.8</v>
@@ -17645,7 +17651,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X44">
         <v>81.8</v>
@@ -17687,7 +17693,7 @@
         <v>4.1</v>
       </c>
       <c r="AK44" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL44">
         <v>235.4</v>
@@ -17708,16 +17714,16 @@
         <v>1.1305</v>
       </c>
       <c r="AR44" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS44">
         <v>2508</v>
       </c>
       <c r="AT44" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU44" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV44">
         <v>74.09999999999999</v>
@@ -17744,13 +17750,13 @@
         <v>7.4</v>
       </c>
       <c r="BD44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE44">
         <v>3.2</v>
       </c>
       <c r="BF44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG44">
         <v>81</v>
@@ -17779,22 +17785,22 @@
         <v>234</v>
       </c>
       <c r="E45" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F45" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G45" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H45" t="s">
         <v>286</v>
       </c>
       <c r="I45" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J45">
-        <v>131.6</v>
+        <v>132.4</v>
       </c>
       <c r="K45">
         <v>5.8</v>
@@ -17833,7 +17839,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X45">
         <v>79</v>
@@ -17875,7 +17881,7 @@
         <v>3</v>
       </c>
       <c r="AK45" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL45">
         <v>121.7</v>
@@ -17896,16 +17902,16 @@
         <v>1.1367</v>
       </c>
       <c r="AR45" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS45">
         <v>2313</v>
       </c>
       <c r="AT45" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU45" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV45">
         <v>70.59999999999999</v>
@@ -17932,13 +17938,13 @@
         <v>5.3</v>
       </c>
       <c r="BD45" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE45">
         <v>4.1</v>
       </c>
       <c r="BF45" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG45">
         <v>78</v>
@@ -17967,25 +17973,25 @@
         <v>235</v>
       </c>
       <c r="E46" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F46" t="s">
         <v>220</v>
       </c>
       <c r="G46" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H46" t="s">
         <v>287</v>
       </c>
       <c r="I46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J46">
-        <v>91.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K46">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -18021,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="X46">
         <v>84.2</v>
@@ -18063,7 +18069,7 @@
         <v>10.7</v>
       </c>
       <c r="AK46" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL46">
         <v>180</v>
@@ -18084,16 +18090,16 @@
         <v>1.1356</v>
       </c>
       <c r="AR46" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS46">
         <v>2248</v>
       </c>
       <c r="AT46" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU46" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV46">
         <v>74.3</v>
@@ -18120,13 +18126,13 @@
         <v>58</v>
       </c>
       <c r="BD46" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BE46">
         <v>20.9</v>
       </c>
       <c r="BF46" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG46">
         <v>86</v>
@@ -18155,25 +18161,25 @@
         <v>235</v>
       </c>
       <c r="E47" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F47" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G47" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H47" t="s">
         <v>287</v>
       </c>
       <c r="I47" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J47">
-        <v>91.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K47">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -18209,7 +18215,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X47">
         <v>81.09999999999999</v>
@@ -18251,7 +18257,7 @@
         <v>12.3</v>
       </c>
       <c r="AK47" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL47">
         <v>90</v>
@@ -18272,16 +18278,16 @@
         <v>1.1421</v>
       </c>
       <c r="AR47" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS47">
         <v>2053</v>
       </c>
       <c r="AT47" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU47" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV47">
         <v>66.09999999999999</v>
@@ -18308,13 +18314,13 @@
         <v>40.4</v>
       </c>
       <c r="BD47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BE47">
         <v>25.5</v>
       </c>
       <c r="BF47" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG47">
         <v>84</v>
@@ -18343,25 +18349,25 @@
         <v>235</v>
       </c>
       <c r="E48" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F48" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G48" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H48" t="s">
         <v>287</v>
       </c>
       <c r="I48" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J48">
-        <v>91.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K48">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -18397,7 +18403,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="X48">
         <v>78.40000000000001</v>
@@ -18439,7 +18445,7 @@
         <v>12.3</v>
       </c>
       <c r="AK48" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL48">
         <v>180</v>
@@ -18460,16 +18466,16 @@
         <v>1.1479</v>
       </c>
       <c r="AR48" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS48">
         <v>1882</v>
       </c>
       <c r="AT48" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU48" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV48">
         <v>69.09999999999999</v>
@@ -18496,13 +18502,13 @@
         <v>45.9</v>
       </c>
       <c r="BD48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BE48">
         <v>18.5</v>
       </c>
       <c r="BF48" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG48">
         <v>80</v>
@@ -18531,25 +18537,25 @@
         <v>235</v>
       </c>
       <c r="E49" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F49" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G49" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H49" t="s">
         <v>287</v>
       </c>
       <c r="I49" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J49">
-        <v>91.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K49">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -18585,7 +18591,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="X49">
         <v>76.7</v>
@@ -18627,7 +18633,7 @@
         <v>14.6</v>
       </c>
       <c r="AK49" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AL49">
         <v>135</v>
@@ -18648,16 +18654,16 @@
         <v>1.1528</v>
       </c>
       <c r="AR49" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS49">
         <v>1724</v>
       </c>
       <c r="AT49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU49" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV49">
         <v>65.5</v>
@@ -18684,13 +18690,13 @@
         <v>66</v>
       </c>
       <c r="BD49" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BE49">
         <v>25</v>
       </c>
       <c r="BF49" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG49">
         <v>78</v>
@@ -18719,22 +18725,22 @@
         <v>236</v>
       </c>
       <c r="E50" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F50" t="s">
         <v>221</v>
       </c>
       <c r="G50" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H50" t="s">
         <v>288</v>
       </c>
       <c r="I50" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J50">
-        <v>88.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K50">
         <v>4.3</v>
@@ -18773,7 +18779,7 @@
         <v>-2.4</v>
       </c>
       <c r="W50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X50">
         <v>65.90000000000001</v>
@@ -18815,7 +18821,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AK50" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL50">
         <v>225</v>
@@ -18836,16 +18842,16 @@
         <v>1.193</v>
       </c>
       <c r="AR50" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS50">
         <v>669</v>
       </c>
       <c r="AT50" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU50" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV50">
         <v>56.8</v>
@@ -18872,13 +18878,13 @@
         <v>0</v>
       </c>
       <c r="BD50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE50">
         <v>7.4</v>
       </c>
       <c r="BF50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG50">
         <v>69</v>
@@ -18907,22 +18913,22 @@
         <v>236</v>
       </c>
       <c r="E51" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F51" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G51" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H51" t="s">
         <v>288</v>
       </c>
       <c r="I51" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J51">
-        <v>88.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K51">
         <v>5.3</v>
@@ -18961,7 +18967,7 @@
         <v>-2.4</v>
       </c>
       <c r="W51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X51">
         <v>64.2</v>
@@ -19003,7 +19009,7 @@
         <v>8</v>
       </c>
       <c r="AK51" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL51">
         <v>225</v>
@@ -19024,16 +19030,16 @@
         <v>1.1976</v>
       </c>
       <c r="AR51" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS51">
         <v>541</v>
       </c>
       <c r="AT51" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU51" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV51">
         <v>54.7</v>
@@ -19060,13 +19066,13 @@
         <v>0</v>
       </c>
       <c r="BD51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE51">
         <v>2.3</v>
       </c>
       <c r="BF51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG51">
         <v>66</v>
@@ -19095,22 +19101,22 @@
         <v>236</v>
       </c>
       <c r="E52" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F52" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G52" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H52" t="s">
         <v>288</v>
       </c>
       <c r="I52" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J52">
-        <v>88.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K52">
         <v>6.3</v>
@@ -19149,7 +19155,7 @@
         <v>-2.4</v>
       </c>
       <c r="W52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X52">
         <v>63.9</v>
@@ -19191,7 +19197,7 @@
         <v>7</v>
       </c>
       <c r="AK52" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL52">
         <v>199.5</v>
@@ -19212,16 +19218,16 @@
         <v>1.1986</v>
       </c>
       <c r="AR52" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS52">
         <v>512</v>
       </c>
       <c r="AT52" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU52" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV52">
         <v>53.3</v>
@@ -19248,13 +19254,13 @@
         <v>0</v>
       </c>
       <c r="BD52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE52">
         <v>2.5</v>
       </c>
       <c r="BF52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG52">
         <v>66</v>
@@ -19283,22 +19289,22 @@
         <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F53" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G53" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H53" t="s">
         <v>288</v>
       </c>
       <c r="I53" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J53">
-        <v>88.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K53">
         <v>7.3</v>
@@ -19337,7 +19343,7 @@
         <v>-2.4</v>
       </c>
       <c r="W53" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X53">
         <v>63.4</v>
@@ -19379,7 +19385,7 @@
         <v>5.9</v>
       </c>
       <c r="AK53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL53">
         <v>189.7</v>
@@ -19400,16 +19406,16 @@
         <v>1.2001</v>
       </c>
       <c r="AR53" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS53">
         <v>466</v>
       </c>
       <c r="AT53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU53" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV53">
         <v>52.1</v>
@@ -19436,13 +19442,13 @@
         <v>0</v>
       </c>
       <c r="BD53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE53">
         <v>1.1</v>
       </c>
       <c r="BF53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG53">
         <v>65</v>
@@ -19471,22 +19477,22 @@
         <v>237</v>
       </c>
       <c r="E54" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F54" t="s">
         <v>222</v>
       </c>
       <c r="G54" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H54" t="s">
         <v>289</v>
       </c>
       <c r="I54" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J54">
-        <v>105.7</v>
+        <v>106.5</v>
       </c>
       <c r="K54">
         <v>4.8</v>
@@ -19525,7 +19531,7 @@
         <v>0.8</v>
       </c>
       <c r="W54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X54">
         <v>78.7</v>
@@ -19567,7 +19573,7 @@
         <v>7.8</v>
       </c>
       <c r="AK54" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL54">
         <v>202.5</v>
@@ -19588,16 +19594,16 @@
         <v>1.147</v>
       </c>
       <c r="AR54" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS54">
         <v>2029</v>
       </c>
       <c r="AT54" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU54" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV54">
         <v>76.2</v>
@@ -19624,13 +19630,13 @@
         <v>0</v>
       </c>
       <c r="BD54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE54">
         <v>13.2</v>
       </c>
       <c r="BF54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG54">
         <v>78</v>
@@ -19659,22 +19665,22 @@
         <v>237</v>
       </c>
       <c r="E55" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F55" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G55" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H55" t="s">
         <v>289</v>
       </c>
       <c r="I55" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J55">
-        <v>105.7</v>
+        <v>106.5</v>
       </c>
       <c r="K55">
         <v>5.8</v>
@@ -19713,7 +19719,7 @@
         <v>0.8</v>
       </c>
       <c r="W55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X55">
         <v>74.59999999999999</v>
@@ -19755,7 +19761,7 @@
         <v>6.7</v>
       </c>
       <c r="AK55" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL55">
         <v>202.5</v>
@@ -19776,16 +19782,16 @@
         <v>1.1564</v>
       </c>
       <c r="AR55" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AS55">
         <v>1746</v>
       </c>
       <c r="AT55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV55">
         <v>70.90000000000001</v>
@@ -19812,13 +19818,13 @@
         <v>0</v>
       </c>
       <c r="BD55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE55">
         <v>1.6</v>
       </c>
       <c r="BF55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG55">
         <v>73</v>
@@ -19847,22 +19853,22 @@
         <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F56" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G56" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H56" t="s">
         <v>289</v>
       </c>
       <c r="I56" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J56">
-        <v>105.7</v>
+        <v>106.5</v>
       </c>
       <c r="K56">
         <v>6.8</v>
@@ -19901,7 +19907,7 @@
         <v>0.8</v>
       </c>
       <c r="W56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X56">
         <v>71.40000000000001</v>
@@ -19943,7 +19949,7 @@
         <v>5.8</v>
       </c>
       <c r="AK56" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL56">
         <v>202.5</v>
@@ -19964,16 +19970,16 @@
         <v>1.1636</v>
       </c>
       <c r="AR56" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS56">
         <v>1527</v>
       </c>
       <c r="AT56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU56" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV56">
         <v>68</v>
@@ -20000,13 +20006,13 @@
         <v>0</v>
       </c>
       <c r="BD56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE56">
         <v>2.8</v>
       </c>
       <c r="BF56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG56">
         <v>70</v>
@@ -20035,22 +20041,22 @@
         <v>237</v>
       </c>
       <c r="E57" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F57" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G57" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H57" t="s">
         <v>289</v>
       </c>
       <c r="I57" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J57">
-        <v>105.7</v>
+        <v>106.5</v>
       </c>
       <c r="K57">
         <v>7.8</v>
@@ -20089,7 +20095,7 @@
         <v>0.8</v>
       </c>
       <c r="W57" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X57">
         <v>70.2</v>
@@ -20131,7 +20137,7 @@
         <v>4.5</v>
       </c>
       <c r="AK57" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL57">
         <v>202.5</v>
@@ -20152,16 +20158,16 @@
         <v>1.1665</v>
       </c>
       <c r="AR57" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AS57">
         <v>1436</v>
       </c>
       <c r="AT57" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV57">
         <v>66.09999999999999</v>
@@ -20188,13 +20194,13 @@
         <v>0</v>
       </c>
       <c r="BD57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE57">
         <v>9</v>
       </c>
       <c r="BF57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG57">
         <v>70</v>
@@ -20223,25 +20229,25 @@
         <v>238</v>
       </c>
       <c r="E58" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F58" t="s">
         <v>223</v>
       </c>
       <c r="G58" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I58" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J58">
-        <v>57.5</v>
+        <v>58.3</v>
       </c>
       <c r="K58">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -20277,7 +20283,7 @@
         <v>-4</v>
       </c>
       <c r="W58" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X58">
         <v>56.5</v>
@@ -20319,7 +20325,7 @@
         <v>19.5</v>
       </c>
       <c r="AK58" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL58">
         <v>270</v>
@@ -20340,16 +20346,16 @@
         <v>1.2234</v>
       </c>
       <c r="AR58" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AS58">
         <v>-133</v>
       </c>
       <c r="AT58" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU58" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV58">
         <v>50.1</v>
@@ -20376,13 +20382,13 @@
         <v>0.4</v>
       </c>
       <c r="BD58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE58">
         <v>11.7</v>
       </c>
       <c r="BF58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG58">
         <v>60</v>
@@ -20411,25 +20417,25 @@
         <v>238</v>
       </c>
       <c r="E59" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F59" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G59" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H59" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I59" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J59">
-        <v>57.5</v>
+        <v>58.3</v>
       </c>
       <c r="K59">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -20465,7 +20471,7 @@
         <v>-4</v>
       </c>
       <c r="W59" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X59">
         <v>55.7</v>
@@ -20507,7 +20513,7 @@
         <v>18.9</v>
       </c>
       <c r="AK59" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL59">
         <v>270</v>
@@ -20528,16 +20534,16 @@
         <v>1.2256</v>
       </c>
       <c r="AR59" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AS59">
         <v>-193</v>
       </c>
       <c r="AT59" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU59" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV59">
         <v>49.6</v>
@@ -20564,13 +20570,13 @@
         <v>0.4</v>
       </c>
       <c r="BD59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE59">
         <v>8.6</v>
       </c>
       <c r="BF59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG59">
         <v>59</v>
@@ -20599,25 +20605,25 @@
         <v>238</v>
       </c>
       <c r="E60" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F60" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H60" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I60" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J60">
-        <v>57.5</v>
+        <v>58.3</v>
       </c>
       <c r="K60">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -20653,7 +20659,7 @@
         <v>-4</v>
       </c>
       <c r="W60" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X60">
         <v>54.9</v>
@@ -20695,7 +20701,7 @@
         <v>17.8</v>
       </c>
       <c r="AK60" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL60">
         <v>247.5</v>
@@ -20716,16 +20722,16 @@
         <v>1.2278</v>
       </c>
       <c r="AR60" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AS60">
         <v>-254</v>
       </c>
       <c r="AT60" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU60" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV60">
         <v>50.5</v>
@@ -20752,13 +20758,13 @@
         <v>0.4</v>
       </c>
       <c r="BD60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE60">
         <v>6.7</v>
       </c>
       <c r="BF60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG60">
         <v>58</v>
@@ -20787,25 +20793,25 @@
         <v>238</v>
       </c>
       <c r="E61" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F61" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I61" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J61">
-        <v>57.5</v>
+        <v>58.3</v>
       </c>
       <c r="K61">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -20841,7 +20847,7 @@
         <v>-4</v>
       </c>
       <c r="W61" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X61">
         <v>54.6</v>
@@ -20883,7 +20889,7 @@
         <v>16</v>
       </c>
       <c r="AK61" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL61">
         <v>247.5</v>
@@ -20904,16 +20910,16 @@
         <v>1.229</v>
       </c>
       <c r="AR61" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AS61">
         <v>-286</v>
       </c>
       <c r="AT61" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU61" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AV61">
         <v>48.5</v>
@@ -20940,13 +20946,13 @@
         <v>0.4</v>
       </c>
       <c r="BD61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BE61">
         <v>5.5</v>
       </c>
       <c r="BF61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG61">
         <v>58</v>
@@ -21097,10 +21103,10 @@
         <v>2673</v>
       </c>
       <c r="P2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R2">
         <v>5</v>
@@ -21153,10 +21159,10 @@
         <v>2406</v>
       </c>
       <c r="P3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R3">
         <v>5</v>
@@ -21209,10 +21215,10 @@
         <v>1784</v>
       </c>
       <c r="P4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -21265,10 +21271,10 @@
         <v>2181</v>
       </c>
       <c r="P5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -21321,10 +21327,10 @@
         <v>1606</v>
       </c>
       <c r="P6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R6">
         <v>5</v>
@@ -21377,10 +21383,10 @@
         <v>1430</v>
       </c>
       <c r="P7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R7">
         <v>5</v>
@@ -21433,10 +21439,10 @@
         <v>2064</v>
       </c>
       <c r="P8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -21489,10 +21495,10 @@
         <v>1669</v>
       </c>
       <c r="P9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -21545,10 +21551,10 @@
         <v>2071</v>
       </c>
       <c r="P10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -21601,10 +21607,10 @@
         <v>1445</v>
       </c>
       <c r="P11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -21657,10 +21663,10 @@
         <v>858</v>
       </c>
       <c r="P12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -21713,10 +21719,10 @@
         <v>858</v>
       </c>
       <c r="P13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R13">
         <v>5</v>
@@ -21769,10 +21775,10 @@
         <v>579</v>
       </c>
       <c r="P14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R14">
         <v>5</v>
@@ -21825,10 +21831,10 @@
         <v>1611</v>
       </c>
       <c r="P15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R15">
         <v>5</v>
@@ -21881,10 +21887,10 @@
         <v>-191</v>
       </c>
       <c r="P16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R16">
         <v>5</v>
